--- a/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,38 +434,456 @@
           <t>copiado_avoid_nan</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4W5t03Zl</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rN4paNle</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orsato d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6Le197C2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A72TGDlt</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jPP565dL</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>A1CicVEU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>YH892O2B</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>zFLwLRZS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8jyraADG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Qu12kvXf</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Qu12kvXf</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>tYVGfTo2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AwXQwGFe</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MVSS7qFe</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A72TGDlt</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,11 +491,7 @@
   ita </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>tjY4uUem</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>tjY4uUem</t>
@@ -652,29 +648,50 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>t4ZkclrT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orsato d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MVSS7qFe</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>tYVGfTo2</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>f9bfyqFM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -685,7 +702,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>bHLf4sq9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -696,41 +713,29 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Qu12kvXf</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -739,7 +744,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>tYVGfTo2</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -747,7 +752,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -756,7 +761,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AwXQwGFe</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -764,7 +769,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -773,7 +778,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>tYVGfTo2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -781,35 +786,35 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MVSS7qFe</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -818,7 +823,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -826,7 +831,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -837,41 +842,29 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -880,10 +873,177 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>A72TGDlt</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A72TGDlt</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AcgUMf0E</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -491,7 +491,11 @@
   ita </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>tjY4uUem</t>
@@ -637,13 +641,22 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Qu12kvXf</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -680,13 +693,22 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>tYVGfTo2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -741,13 +763,22 @@
       <c r="B16" t="n">
         <v>1</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Qu12kvXf</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -758,13 +789,22 @@
       <c r="B17" t="n">
         <v>1</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghersini d 
+  ita </t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>tSiEeKvS</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -775,13 +815,22 @@
       <c r="B18" t="n">
         <v>1</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>tYVGfTo2</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -789,10 +838,25 @@
           <t>bs5ow5pA</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>IZezRssA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -803,13 +867,22 @@
       <c r="B20" t="n">
         <v>1</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>MLVBCoYg</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -820,13 +893,22 @@
       <c r="B21" t="n">
         <v>1</v>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>MVSS7qFe</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -834,10 +916,25 @@
           <t>6sP22LDL</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -845,10 +942,25 @@
           <t>bepKi4a3</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -856,10 +968,25 @@
           <t>ILr8tvi2</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -870,13 +997,22 @@
       <c r="B25" t="n">
         <v>1</v>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>EJLKYOzb</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -887,13 +1023,22 @@
       <c r="B26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>n10g3KfJ</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GOfxrOoF</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -904,13 +1049,22 @@
       <c r="B27" t="n">
         <v>1</v>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>A72TGDlt</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -918,10 +1072,25 @@
           <t>8KfYbJz0</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -929,9 +1098,15 @@
           <t>EL1P0u6m</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>n3jv1PNN</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -940,10 +1115,25 @@
           <t>M5TEBdK5</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>IB8Kk2vH</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -954,13 +1144,22 @@
       <c r="B31" t="n">
         <v>1</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>A72TGDlt</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -968,10 +1167,25 @@
           <t>WvwvCQVo</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -988,7 +1202,11 @@
   ita </t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>AcgUMf0E</t>
@@ -1012,10 +1230,25 @@
           <t>SORbFvLt</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EZS2ir7i</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1026,13 +1259,22 @@
       <c r="B36" t="n">
         <v>1</v>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>n10g3KfJ</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1040,9 +1282,15 @@
           <t>IXMN9zkI</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
     </row>
   </sheetData>

--- a/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/italy/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -735,7 +735,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -746,7 +746,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
